--- a/banco_de_dados.xlsx
+++ b/banco_de_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,7 @@
           <t>3066</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +440,7 @@
           <t>2184</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +453,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -463,6 +466,7 @@
           <t>2184</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -475,6 +479,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -487,6 +492,11 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -499,6 +509,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -511,6 +522,11 @@
           <t>3353</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -523,6 +539,7 @@
           <t>3353</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -535,6 +552,7 @@
           <t>3066</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -547,6 +565,7 @@
           <t>3353</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -559,6 +578,11 @@
           <t>3339</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -571,6 +595,11 @@
           <t>3066</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -583,6 +612,11 @@
           <t>3066</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -595,6 +629,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -607,6 +642,11 @@
           <t>2184</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -619,6 +659,7 @@
           <t>3066</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -631,6 +672,7 @@
           <t>6102</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -643,6 +685,7 @@
           <t>6102</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -655,6 +698,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -667,6 +711,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -679,6 +724,11 @@
           <t>2184</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -691,6 +741,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -703,6 +754,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -715,6 +767,7 @@
           <t>6102</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -727,6 +780,11 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -739,6 +797,7 @@
           <t>2184</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -751,6 +810,11 @@
           <t>3066</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -763,6 +827,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -775,6 +840,7 @@
           <t>2135</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/banco_de_dados.xlsx
+++ b/banco_de_dados.xlsx
@@ -492,11 +492,7 @@
           <t>2135</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -522,11 +518,7 @@
           <t>3353</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -578,11 +570,7 @@
           <t>3339</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -595,11 +583,7 @@
           <t>3066</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -612,11 +596,7 @@
           <t>3066</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -642,11 +622,7 @@
           <t>2184</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -724,11 +700,7 @@
           <t>2184</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -780,11 +752,7 @@
           <t>2135</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -810,11 +778,7 @@
           <t>3066</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/banco_de_dados.xlsx
+++ b/banco_de_dados.xlsx
@@ -492,7 +492,11 @@
           <t>2135</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -518,7 +522,11 @@
           <t>3353</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -570,7 +578,11 @@
           <t>3339</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -583,7 +595,11 @@
           <t>3066</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -596,7 +612,11 @@
           <t>3066</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -622,7 +642,11 @@
           <t>2184</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -700,7 +724,11 @@
           <t>2184</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -752,7 +780,11 @@
           <t>2135</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -778,7 +810,11 @@
           <t>3066</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">

--- a/banco_de_dados.xlsx
+++ b/banco_de_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,149 @@
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>110401 - Armazenamento, depósito, guarda de bens de qualquer espécie.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>260101 - Serviços de coleta, remessa ou entrega de correspondências, documentos, objetos, bens ou valores, inclusive pelos correios e suas agências franqueadas.</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>171401 - Advocacia</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>010601 - Assessoria e consultoria em informática.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>070901 - VARRIÇÃO, COLETA, REMOÇÃO, INCINERAÇÃO, TRATAMENTO, RECICLAGEM, SEPARAÇÃO E DESTINAÇÃO FINAL DE LIXO, REJEITOS E OUTROS RESÍDUOS QUAISQUER.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>170201 - Datilografia, digitação, estenografia e congêneres.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>042201 - Planos de medicina de grupo ou individual e convênios para prestação de assistência médica, hospitalar, odontológica e congêneres.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>071301 - Dedetização, desinfecção, desinsetização, imunização, higienização, desratização, pulverização e congêneres.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>071001 - Limpeza, manutenção e conservação de vias e logradouros públicos, parques, jardins e congêneres.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados.xlsx
+++ b/banco_de_dados.xlsx
@@ -813,11 +813,7 @@
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -826,11 +822,7 @@
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -839,11 +831,7 @@
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -852,11 +840,7 @@
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -865,11 +849,7 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -878,11 +858,7 @@
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -891,11 +867,7 @@
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -904,11 +876,7 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -917,11 +885,7 @@
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -930,11 +894,7 @@
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -943,11 +903,7 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
